--- a/Practica_02/Data_Practica_02.xlsx
+++ b/Practica_02/Data_Practica_02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjamin/Documents/Personal/Cursos_Tec/Econometría II/Econometria-II-2025-Tec/Practica_02/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1748D8E3-372E-5A46-8CD5-05E16A2F5AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D00DEB6-F6D5-EE4B-BC6F-3BA256CE61FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="252">
   <si>
     <t>Periodos</t>
   </si>
@@ -773,6 +773,9 @@
   </si>
   <si>
     <t>TDesocupa_H</t>
+  </si>
+  <si>
+    <t>TDesocupa_M</t>
   </si>
 </sst>
 </file>
@@ -825,6 +828,3203 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-MX"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Datos!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TDesocupa</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Datos!$C$2:$C$248</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="247"/>
+                <c:pt idx="0">
+                  <c:v>3.7527340184310001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.60125868093</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.6994267452230001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.6176306361020001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.8376402394269999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.834287397667</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.650788706827</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.4533965640109998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.4523271087510001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.2424616790509999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.025450857879</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.1084047624540001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.2544586295259998</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.5348886905170001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.2932439738450001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.4138679758829999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.3674164483569999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.5605400072100002</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.683969734677</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.6516553652870001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.6546149493270002</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3.7169112242779998</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3.7983595634310001</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3.8449912114120002</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3.725673000659</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3.8797546386190001</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3.857998437475</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3.747763625078</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3.605258384911</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3.5413814662849998</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3.5009526340449999</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>3.5978327706190001</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3.516805309515</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>3.6793947667669999</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>3.5131719315629999</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>3.6583992284239999</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3.8891185568550002</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>3.6438754771620001</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3.6979292780090001</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>3.6002528468750001</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3.6478886389720002</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>3.654523294569</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>3.8480383609489999</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>3.8113654637779999</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>3.8577314785230001</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>3.9589409140490002</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>4.6839574843960001</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>4.5089557595730003</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>4.6532646367519996</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>5.0035659744979997</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>5.0438109301549998</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>5.3269160476269999</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>5.6556562995709996</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>5.4574057020040003</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5.6168748682030003</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5.7405847870180002</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5.8969988736519996</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5.5900306477069996</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5.3607265835810001</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>5.2661661709649996</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>5.5231137750199997</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5.2277810642910003</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>5.2684189021929999</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>5.4643033817379996</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>5.25823917631</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>5.1928529073469996</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>5.3235094325850003</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>4.9714024809710002</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>5.2138664287159999</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>5.4193363285779999</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>5.3462460818290003</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>5.4709623620779997</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>5.1106055380850002</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>5.2837578950620001</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>5.0601109793330004</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>5.1707536843249997</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>5.3522659647330002</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>5.5783572924279996</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>5.2735299690390001</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>5.3400754563149997</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>5.2401143122529996</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>4.8105539002419997</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>5.0613154158739997</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>5.0263679830269998</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>4.6688701157560004</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>5.4205465374359996</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>5.1160355837280003</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>4.8903573833909997</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>4.8770862176390004</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>4.8546605310080002</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>4.7232691892930001</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>4.9394476198569999</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>4.6713797343719996</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>4.8355590770659997</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>5.2058233929169999</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>4.9752407398939997</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>5.1567084506540004</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>4.9593289903280002</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>5.0499144513500003</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>5.118855965931</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>4.958620628607</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>5.0711270901269998</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>4.8956712432679996</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>4.8219002144590002</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>4.9841503846329998</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>4.8834677652879996</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>4.6093572876989999</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>4.7934149226459999</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>4.9064324611729999</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>4.8195445324669999</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>5.2859564294770003</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>4.9174295039449998</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>4.9421407304929996</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>4.8266428154050001</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>5.2163307478169996</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>4.842706671707</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>4.7839556280310003</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>4.6471617342789999</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>4.6555332172890003</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>4.1682498191789996</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>4.3920907194170002</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>4.44689796716</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>4.2755455350049996</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>4.3478302732060001</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>4.3855234725210002</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>4.4133905098200001</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>4.4910786090899997</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>4.3868694938489998</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>4.1955897896580003</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>4.4418772701410001</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>4.0642037097739996</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>4.3069920539459998</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>4.1719148407729998</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>4.2551355173700003</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>4.143935141</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>3.8231602386830001</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>3.9539665233510002</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>3.9216349093030001</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>3.8113709198230001</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>3.7626804749509999</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>3.8439902401560002</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>3.5848950034549998</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>3.5937928067740001</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>3.6365523591460001</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>3.5361056961439998</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>3.46886300247</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>3.5269526146420001</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>3.4758683862169999</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>3.5077006670949999</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>3.2766958753290001</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>3.2562404176270001</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>3.3331283025170002</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>3.3404917462769999</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>3.444029270628</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>3.4998122407980001</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>3.3908798105560001</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>3.2831122483390001</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>3.2929554017179998</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>3.26555678258</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>3.3830721188370001</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>3.2240305283750001</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>3.354079389722</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>3.2933047901950001</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>3.2685925820709998</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>3.3302382870159999</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>3.2009966760780002</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>3.3415843103810001</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>3.6599842011470001</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>3.4556861252050002</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>3.3923398652849999</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>3.6146266992729998</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>3.4855124914169999</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>3.5390888120419999</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>3.5337335847319999</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>3.524910119012</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>3.4830534152169998</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>3.5179026948229999</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>3.6129166667089998</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>3.531357129936</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>3.196139088407</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>3.6483041440989998</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>3.5747240912990002</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>3.3215680638820002</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>4.6741323190479998</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>4.2798737073720003</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>5.4392870120219996</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>5.0087617310740002</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>4.9020729797270004</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>4.7916484147459997</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>4.5866654381809999</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>4.5120987913009998</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>4.1710985969990002</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>4.5353529536600004</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>4.4476618689459997</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>4.4664952814190002</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>4.6677912386270002</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>4.0755942321890002</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>3.9752773616370001</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>4.0829306876020004</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>4.0010618402900002</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>3.9199185074180001</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>3.8449728300200001</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>3.8041887198039999</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>3.8113036511730001</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>3.577387595721</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>3.8266890082340002</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>3.480301973205</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>3.0641773901780001</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>3.3172544467480001</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>3.304225633797</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>3.186525267266</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>3.2412225604049998</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>3.1254239678909999</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>3.214792762049</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>2.9415998261120002</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>2.9678965903260002</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>2.9067911082219999</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>2.8433249630790001</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>2.8246801205579999</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>2.8697179845090002</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>2.9301116374479999</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>2.6061284956550002</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>2.900619158574</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>2.6944020296810001</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>2.694303834761</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>2.6823868763390002</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>2.792605250831</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>2.796399259123</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>2.7716186712819999</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>2.5992041323340001</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>2.7049350223439999</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>2.6695666456240001</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>2.599636493827</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>2.717188715941</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>2.7062083149570002</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>2.7625172451669999</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>2.73468593569</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>2.4501563734760001</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>2.704021647042</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>2.6208857766040001</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>2.625449668096</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>2.6663779057310002</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>2.6329321267960002</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>2.6073488948749999</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>2.7001323580290002</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>2.6235498280530001</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>2.5630947592950002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D175-6541-AE0B-ECF9AC19FF46}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Datos!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TDesocupa_H</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Datos!$D$2:$D$248</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="247"/>
+                <c:pt idx="0">
+                  <c:v>3.4558818272740002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.3118299616260001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.3145747771480001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.3676610150689998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.7831497116010002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.7427590468259999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.2950178089129998</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.1214884736099999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.4594284310500001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.9184259351119999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.91037583525</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.9595739795339999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.0968621438690001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.548770218584</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.1903129480439998</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.1169985651999998</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.1299027933949999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.3597907420499999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.3116929005840001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.4907548110589999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.5307570680559999</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3.3396565747559999</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3.6163286586860002</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3.6054282591360001</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3.4835295743439998</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3.5766222067440001</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3.5918117693389999</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3.6365046299869999</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3.4161305546089999</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3.2550653665759999</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3.3782326100160001</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>3.3133220700670001</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3.242288004278</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>3.4967256638289999</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>3.1508369092959998</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>3.4861484129279998</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3.7965032335290001</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>3.4704455161540002</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3.5400183480730001</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>3.3999905645249999</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3.4759872459980001</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>3.3271017398630001</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>3.824422345761</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>3.8745635170039998</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>3.7812491975890001</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>4.1110536043449999</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>4.86647076638</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>4.3076965273249996</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>4.4338123261489999</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>5.122077310111</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>5.244920979392</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>5.6307258747370001</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>5.8981183878690002</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>5.6075283705299999</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5.5730367541249999</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5.3625462028479998</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5.6348053374070002</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5.5541684673239997</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5.3999791982760001</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>5.3682592544850003</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>5.7196253810390001</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5.307167762672</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>5.1921499493740004</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>5.529598583227</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>5.1927117586050002</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>5.367332001606</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>5.3636766652399999</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>4.8133407898889997</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>5.3280832929280004</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>5.591473235024</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>5.5594180977220002</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>5.6821047852230002</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>5.2017864231550002</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>5.3802473241569997</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>5.1961341501109999</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>5.1335585203549998</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>5.4186652377559996</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>5.4036711627000003</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>5.2470167464069997</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>5.2269793778139997</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>5.0628843116019997</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>4.8578350667699999</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>5.012023399447</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>5.0512512735039996</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>4.5683848529570001</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>5.691209511696</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>5.1919704108689997</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>4.8346009736319999</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>4.8387551826450004</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>4.8916434910730002</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>4.7163194720329997</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>4.9637967853739999</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>4.4547103174649996</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>4.783818946937</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>5.153337196831</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>4.9610813806790004</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>5.1494896238820003</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>4.8110740218219998</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>4.9310859292610001</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>5.1870793525809997</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>5.0176085390359999</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>4.9106145436339999</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>4.8479945062430003</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>4.8319806530070002</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>4.8843334113249997</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>4.9245725791410004</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>4.6547977426990004</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>4.6190166352819997</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>4.8506635966119998</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>4.7683197518130003</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>5.0529470705820003</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>5.1000495986640004</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>4.8554305922590002</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>4.9104353667279996</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>5.313673301653</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>4.7879065650039996</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>4.8371048845370002</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>4.6148369411239996</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>4.6533045911339999</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>4.091494382604</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>4.3977196987170002</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>4.451243081456</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>4.1232232025310003</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>4.2076632111540002</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>4.2724652589270002</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>4.1294961823729999</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>4.2901973590680003</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>4.3281969151790003</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>4.1130758428969996</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>4.2147588866449999</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>4.030101878969</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>4.2437953548560001</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>4.1133475212809998</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>4.13523982274</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>4.185748173675</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>3.8432726479769999</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>3.9134065467460002</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>3.8631042888830001</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>3.7718961127199999</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>3.6733328842869999</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>3.6642851709470001</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>3.60269608692</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>3.6873332274999999</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>3.5453956467949999</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>3.3536723172570002</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>3.451166205057</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>3.3353372852050001</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>3.314768303658</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>3.3562026338790001</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>3.1715889476550001</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>3.2728008001100002</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>3.1728075224080001</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>3.3147875204539998</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>3.2899425641329998</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>3.1730742761149999</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>3.3896499878280002</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>3.2823579470389999</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>3.1247687749890001</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>3.2119506277249998</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>3.4105387900270001</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>3.2435196502079999</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>3.406113385372</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>3.1515776571240002</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>3.0797228183200001</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>3.1423246663629998</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>2.9939510631980002</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>3.295151243896</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>3.613077389781</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>3.3180321754539999</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>3.2841338287389998</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>3.5126701173899999</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>3.4569853672050002</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>3.442446460612</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>3.4722009900159998</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>3.43007170435</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>3.6503692494200002</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>3.5307554985770002</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>3.6390496663270002</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>3.450061658074</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>3.2098141200570001</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>3.5134407548729998</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>3.5358383995590001</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>3.2413634705369998</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>5.0117739718480001</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>5.2544276940429997</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>5.7863587741769997</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>4.6122125594619998</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>5.0600669821919997</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>5.1338399080489996</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>4.6774261371339998</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>4.9141994998019998</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>4.0794746134100004</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>4.5340579136030001</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>4.526979207398</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>4.5033902865490001</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>5.0452050536820003</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>4.1509739394479999</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>3.9986292789040001</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>3.9582583215399998</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>4.0034241105410002</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>3.832967092309</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>3.8933270752250002</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>3.6690075540640001</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>3.4945612650059998</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>3.655468376989</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>3.7306464187119999</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>3.5236372214629998</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>3.1169881428799999</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>3.26338327194</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>3.362508440309</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>3.1704931119899999</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>3.2150058814600002</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>3.086790146732</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>3.0851853669490001</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>2.858273871902</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>3.0820546877820001</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>2.9543949103389999</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>2.556807942591</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>2.9289956847440002</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>2.9323330992229999</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>2.8480430679030002</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>2.6050386946750002</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>3.0423356843409999</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>2.6621854128639999</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>2.6558388616070001</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>2.7349055136090001</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>2.8185020497490001</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>2.7227411245500002</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>2.7315004756289998</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>2.4801108824910001</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>2.5613801589679999</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>2.637879144842</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>2.6836857357869999</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>2.7321319777639999</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>2.8020121079129998</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>2.6896384352620002</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>2.701270099876</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>2.409543977522</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>2.6560379527050002</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>2.6720309379240001</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>2.4811742206130001</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>2.6462877336870001</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>2.5693878111499999</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>2.4940392537389999</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>2.6206829705480001</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>2.5545742839029999</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>2.527955220715</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D175-6541-AE0B-ECF9AC19FF46}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Datos!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TDesocupa_M</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Datos!$E$2:$E$248</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="247"/>
+                <c:pt idx="0">
+                  <c:v>4.2635795597759998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.0878935741399998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.3301325047860004</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.0311121118419999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.951122436611</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.9031298732269999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.446791806886</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.913449059825</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.5277975395180001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.6682537547840002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.2825843670650001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.299917470424</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.4933312750850001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.531117778149</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.4681298501529998</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.900865414599</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.789114560242</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.802889852946</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4.4333392207799998</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.8330615559629999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.9348057583139999</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.1897380103900002</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4.1678643096699997</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4.2816305531839998</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4.0925948083790002</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>4.4664881472440001</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>4.3149094032640001</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3.9593229565039998</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3.9283407652750002</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3.8872367393939999</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3.8135804834079998</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>3.9788208096500002</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>4.0028768174360003</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>3.8530762269440002</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>4.1543918238020003</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>4.0084510743669997</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>4.0120430622540004</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>3.9877411417830002</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>4.0014423626009998</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>3.975595333117</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3.940140308278</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>4.0624792396259997</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>3.94474789099</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>3.6507814510990002</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>4.0108655214100004</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>3.5881683981110002</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>4.3703354238439998</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>5.0035745915299996</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>5.0260552224000001</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>4.8460206719150003</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>4.7769831015199999</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>4.926046516055</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>5.2688363550349999</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>5.019767851438</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5.7085059666770004</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>6.1940683015499998</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>6.2765412942890002</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5.569513640696</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5.3013966865300004</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>5.2096802922550003</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>5.2226245288799999</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5.0908238800090002</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>5.4186830265849997</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>5.4490307418219999</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>5.395267082668</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>4.8164948256490003</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>5.2240361574499996</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>5.1385067048990001</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>4.9798754038080002</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>5.0842034408380004</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>4.9972926913929996</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>5.2615593439069999</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>4.9920760152200003</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>5.1161201123330002</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>4.8020316146309998</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>5.2657047311329999</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>5.2346999829509997</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>5.867036541199</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>5.2892852066209999</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>5.4406232123080001</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>5.4194037617069997</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>4.7650524961420002</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>5.1998917184850004</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>5.0709236737810004</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>4.9064620819589999</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>4.9616787441770001</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>4.9268153239419998</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>4.9637289828110003</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>4.9321515398880003</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>4.8841113066880002</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>4.7001639628429999</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>4.8453528716449998</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>4.906755382849</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>4.9813410116989996</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>5.3759911312610003</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>5.001135210937</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>5.2366757357260001</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>5.171329749481</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>5.1615129140339997</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>4.9657191669680003</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>4.8641271217410003</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>5.4306934555739996</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>4.9343047305500001</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>4.7777130681840001</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>5.0745823104610004</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>4.8711351010400001</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>4.6349652929499996</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>5.0484080202339996</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>5.0401006105870003</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>4.8909119389990003</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>5.5558294190020003</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>4.5770796304800001</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>5.0986120195869997</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>4.7972343219539999</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>4.9825585714010003</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>4.9182894860150004</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>4.6781262718820003</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>4.7090982252220002</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>4.8160342987930003</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>4.3014761408329996</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>4.384312141204</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>4.3927109672620004</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>4.4524753928129996</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>4.5777149850840004</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>4.561645358961</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>4.9074786941199999</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>4.7174457224769997</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>4.4593307847480004</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>4.3729300946379999</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>4.770744313362</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>4.2793081002709998</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>4.4669293065340003</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>4.2428005375259996</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>4.4030122953579998</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>4.0148646149919998</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>3.7936270203459999</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>3.994981297936</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>4.0377625112870001</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>3.7888999253179998</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>3.8688101091210001</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>4.2095202337959998</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>3.5252683629849999</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>3.6185703747</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>3.8445951129520002</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>3.7896879254570002</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>3.412998733297</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>3.815107800701</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>3.7869475153519998</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>3.7335232825009999</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>3.445676508159</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>3.1810971134799999</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>3.545142595118</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>3.4548464728449999</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>3.656410568678</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>4.1846131613980004</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>3.387485290941</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>3.2257968698530002</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>3.5058542633940002</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>3.3258516726080001</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>3.4026425616039999</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>3.1821355187420002</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>3.2722970756079999</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>3.4951952323879998</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>3.5188053227310001</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>3.700119184903</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>3.5126329213749998</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>3.5597094226579999</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>3.6629910735400002</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>3.6011838986520002</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>3.4837125923130001</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>3.742821670393</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>3.6474133944689999</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>3.7018562437639999</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>3.6468985702099999</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>3.6680020158929998</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>3.2015247817549999</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>3.549655657677</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>3.5795362630019998</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>3.749634407571</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>3.0782877792050001</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>3.7770050440320002</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>3.5499814729970001</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>3.4053282115319998</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>4.3042206876379998</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>2.7811779180820002</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>4.9444774788489996</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>5.7075136967700004</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>4.6072191344649998</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>4.264260090694</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>4.4853801327080003</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>3.9668381036399998</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>4.2211732905280002</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>4.4293797202469998</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>4.1498302437149999</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>4.3629994173249997</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>4.2569803413159999</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>3.9578669539070002</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>3.9948450158550002</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>4.3280166176119996</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>3.9463894148310001</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>4.0546867630480001</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>3.8342922581150001</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>4.0061543942239997</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>4.3596491868970002</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>3.384244033446</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>3.8036243541050001</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>3.3876185755820001</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>3.0937356641189999</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>3.352546518454</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>3.2818875350950001</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>3.2580767888710001</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>3.24459569371</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>3.1692003045970001</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>3.4830114683339999</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>3.047976616908</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>2.8600506014609999</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>2.7813565999629999</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>3.1089283191280002</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>2.6625353921229999</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>2.850631189045</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>2.9845654565170001</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>2.6693272536319999</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>2.731573575549</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>2.721000278255</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>2.7310787284379998</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>2.6718433743030001</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>2.7418420045479999</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>2.9774512755110001</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>2.7930793202049999</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>2.6488637124349999</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>2.9029072825900002</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>2.7406123572759999</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>2.42656616315</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>2.7710074331490002</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>2.6107039724550001</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>2.8486672004120002</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>2.7660573044240002</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>2.5849301999329999</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>2.757375236019</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>2.5355935010169999</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>2.8011494516959998</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>2.6171836396880002</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>2.7049856812200002</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>2.7748487322309998</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>2.7922159727750002</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>2.796118918755</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>2.6687147296720002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-D175-6541-AE0B-ECF9AC19FF46}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1907327168"/>
+        <c:axId val="1907284528"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1907327168"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1907284528"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1907284528"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1907327168"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-MX"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>368300</xdr:colOff>
+      <xdr:row>228</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>812800</xdr:colOff>
+      <xdr:row>242</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A174A410-6B8F-E95B-F0E6-0E3F1B68F200}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1161,7 +4361,7 @@
         <v>250</v>
       </c>
       <c r="E1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -5365,5 +8565,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>